--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -77,7 +77,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="146">
   <si>
     <t>Property</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Mapping du modèle logique métier entre CDA et FHIR</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -77,7 +74,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -224,7 +221,7 @@
     <t>ClinicalDocument.documentationOf.serviceEvent.lab:statusCode</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-Composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
   </si>
   <si>
     <t>Composition.meta.profile</t>
@@ -254,7 +251,7 @@
     <t>Composition.status</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/PatientDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Patient</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-record-target</t>
@@ -275,7 +272,7 @@
     <t>Composition.subject</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/AuteurDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Auteur</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-author</t>
@@ -296,7 +293,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/InformateurDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Informateur</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-informant</t>
@@ -311,7 +308,7 @@
     <t>informant</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/StructureConservationDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/StructureConservation</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-custodian</t>
@@ -326,7 +323,7 @@
     <t>custodian</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DestinatairePrevuDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/DestinatairePrevu</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-information-recipient</t>
@@ -341,7 +338,7 @@
     <t>informationRecipient</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ResponsableDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Responsable</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-legal-authenticator</t>
@@ -353,7 +350,7 @@
     <t>Responsable du docuement</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ValidateurDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Validateur</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-authenticator</t>
@@ -383,7 +380,7 @@
     <t>dataEnterer</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ParticipantDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Participant</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-participant</t>
@@ -413,7 +410,7 @@
     <t>inFulfillmentOf</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/EvenementDocumente</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Evenement</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-documentation-of</t>
@@ -443,7 +440,7 @@
     <t>relatedDocument</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/ConsentementDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Consentement</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-authorization</t>
@@ -648,74 +645,74 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -731,50 +728,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>99</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>102</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -790,50 +787,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>104</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>106</v>
-      </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -849,50 +846,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -908,50 +905,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -967,50 +964,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>118</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1026,50 +1023,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>123</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1085,50 +1082,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>128</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1144,50 +1141,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1203,50 +1200,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1262,50 +1259,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>143</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1321,185 +1318,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>32</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>36</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>39</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>42</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B6" t="s" s="2">
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>44</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>45</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>54</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
         <v>59</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -1515,152 +1512,152 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -1676,50 +1673,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1735,48 +1732,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1792,50 +1789,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>83</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>85</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1851,48 +1848,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1908,50 +1905,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>92</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1967,50 +1964,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>28</v>
       </c>
-      <c r="D1" t="s" s="1">
-        <v>29</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="E2" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="B3" t="s" s="2">
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>96</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>97</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -74,7 +74,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MappingModeleMetierCDAFHIR</t>
+    <t>Mapping du modèle logique métier de l'en-tête : CDA, FHIR</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -10,13 +10,12 @@
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
     <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
-    <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="107">
   <si>
     <t>Property</t>
   </si>
@@ -39,12 +38,15 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mapping du modèle logique métier de l'en-tête : CDA, FHIR</t>
+    <t>Mapping du modèle logique métier de l'en-tête/CDA/FHIR</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
+    <t>Mapping du modèle logique métier de l'en-tête /CDA / FHIR</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +86,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping entre les éléments du modèle logique métier utilisés en CDA et leurs équivalents en FHIR.</t>
+    <t>Ce ConceptMap présente trois groupes de mapping :
+ - Groupe Mapping 1 : entre le modèle logique métier de l'en-tête et les éléments CDA
+ - Groupe Mapping 2 et Groupe Mapping 3 : entre les éléments CDA et les éléments FHIR</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -111,162 +115,162 @@
     <t/>
   </si>
   <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-clinical-document</t>
+  </si>
+  <si>
+    <t>EnteteDocument.identifiantUniqueDocument</t>
+  </si>
+  <si>
+    <t>equivalent</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.id</t>
+  </si>
+  <si>
+    <t>EnteteDocument.modeleDocument</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.templateId</t>
+  </si>
+  <si>
+    <t>EnteteDocument.typeDocument</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.code</t>
+  </si>
+  <si>
+    <t>EnteteDocument.titre</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.title</t>
+  </si>
+  <si>
+    <t>EnteteDocument.dateDeCreation</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.effectiveTime</t>
+  </si>
+  <si>
+    <t>EnteteDocument.niveauConfidentialite</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.confidentialityCode</t>
+  </si>
+  <si>
+    <t>EnteteDocument.languePrincipaleDocument</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.languageCode</t>
+  </si>
+  <si>
+    <t>EnteteDocument.identifiantDuLotDeVersions</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.setId</t>
+  </si>
+  <si>
+    <t>EnteteDocument.versionDocument</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.versionNumber</t>
+  </si>
+  <si>
+    <t>EnteteDocument.StatutDocument</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.documentationOf.serviceEvent.statusCode</t>
+  </si>
+  <si>
+    <t>EnteteDocument.patient</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.recordTarget</t>
+  </si>
+  <si>
+    <t>EnteteDocument.auteur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.author</t>
+  </si>
+  <si>
+    <t>EnteteDocument.operateurSaisie</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.dataEnterer</t>
+  </si>
+  <si>
+    <t>EnteteDocument.informateur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.informant</t>
+  </si>
+  <si>
+    <t>EnteteDocument.structureConservation</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.custodian</t>
+  </si>
+  <si>
+    <t>EnteteDocument.destinataire</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.informationRecipient</t>
+  </si>
+  <si>
+    <t>EnteteDocument.responsable</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>EnteteDocument.validateur</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.authenticator</t>
+  </si>
+  <si>
+    <t>EnteteDocument.participant</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.participant</t>
+  </si>
+  <si>
+    <t>EnteteDocument.associationPrescription</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.inFulfillmentOf</t>
+  </si>
+  <si>
+    <t>EnteteDocument.evenement</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.documentationOf</t>
+  </si>
+  <si>
+    <t>EnteteDocument.documentReference</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.relatedDocument</t>
+  </si>
+  <si>
+    <t>EnteteDocument.consentementAssocie</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.authorization</t>
+  </si>
+  <si>
+    <t>EnteteDocument.associationPriseEncharge</t>
+  </si>
+  <si>
+    <t>ClinicalDocument.componentOf</t>
+  </si>
+  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-bundle-document</t>
   </si>
   <si>
-    <t>EnteteDocument.identifiantUniqueDocument</t>
-  </si>
-  <si>
-    <t>equivalent</t>
-  </si>
-  <si>
     <t>Bundle.identifier</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-clinical-document</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.id</t>
-  </si>
-  <si>
-    <t>EnteteDocument.modeleDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.templateId</t>
-  </si>
-  <si>
-    <t>EnteteDocument.typeDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.code</t>
-  </si>
-  <si>
-    <t>EnteteDocument.titre</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.title</t>
-  </si>
-  <si>
-    <t>EnteteDocument.dateDeCreation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.effectiveTime</t>
-  </si>
-  <si>
-    <t>EnteteDocument.niveauConfidentialite</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.confidentialityCode</t>
-  </si>
-  <si>
-    <t>EnteteDocument.languePrincipaleDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.languageCode</t>
-  </si>
-  <si>
-    <t>EnteteDocument.identifiantDuLotDeVersions</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.setId</t>
-  </si>
-  <si>
-    <t>EnteteDocument.versionDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.versionNumber</t>
-  </si>
-  <si>
-    <t>EnteteDocument.StatutDocument</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.documentationOf.serviceEvent.statusCode</t>
-  </si>
-  <si>
-    <t>EnteteDocument.patient</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.recordTarget</t>
-  </si>
-  <si>
-    <t>EnteteDocument.auteur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.author</t>
-  </si>
-  <si>
-    <t>EnteteDocument.operateurSaisie</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.dataEnterer</t>
-  </si>
-  <si>
-    <t>EnteteDocument.informateur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.informant</t>
-  </si>
-  <si>
-    <t>EnteteDocument.structureConservation</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.custodian</t>
-  </si>
-  <si>
-    <t>EnteteDocument.destinataire</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.informationRecipient</t>
-  </si>
-  <si>
-    <t>EnteteDocument.responsable</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>EnteteDocument.validateur</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.authenticator</t>
-  </si>
-  <si>
-    <t>EnteteDocument.participant</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.participant</t>
-  </si>
-  <si>
-    <t>EnteteDocument.associationPrescription</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.inFulfillmentOf</t>
-  </si>
-  <si>
-    <t>EnteteDocument.evenement</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.documentationOf</t>
-  </si>
-  <si>
-    <t>EnteteDocument.documentReference</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.relatedDocument</t>
-  </si>
-  <si>
-    <t>EnteteDocument.consentementAssocie</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.authorization</t>
-  </si>
-  <si>
-    <t>EnteteDocument.associationPriseEncharge</t>
-  </si>
-  <si>
-    <t>ClinicalDocument.componentOf</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
   </si>
   <si>
@@ -303,25 +307,25 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t>Composition.data-enterer-extension</t>
-  </si>
-  <si>
-    <t>Composition.informant-extension</t>
+    <t>Composition.DataEntererExtension</t>
+  </si>
+  <si>
+    <t>Composition.extension:InformantExtension</t>
   </si>
   <si>
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t>Composition.information-recipient-extension</t>
+    <t>Composition.extension:InformationRecipientExtension</t>
   </si>
   <si>
     <t>Composition.attester</t>
   </si>
   <si>
-    <t>Composition.participant-extension</t>
-  </si>
-  <si>
-    <t>Composition.order-extension</t>
+    <t>Composition.extension:ParticipantExtension</t>
+  </si>
+  <si>
+    <t>Composition.extension:OrderExtension</t>
   </si>
   <si>
     <t>Composition.event</t>
@@ -330,7 +334,7 @@
     <t>Composition.relatesTo</t>
   </si>
   <si>
-    <t>Composition.consent-extension</t>
+    <t>Composition.extension:ConsentExtension</t>
   </si>
   <si>
     <t>Composition.encounter</t>
@@ -511,74 +515,74 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -589,55 +593,354 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E26" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -651,48 +954,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -703,695 +1006,339 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>26</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E26" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2"/>
     </row>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,8 +87,9 @@
   </si>
   <si>
     <t>Ce ConceptMap présente trois groupes de mapping :
- - Groupe Mapping 1 : entre le modèle logique métier de l'en-tête et les éléments CDA
- - Groupe Mapping 2 et Groupe Mapping 3 : entre les éléments CDA et les éléments FHIR</t>
+ - Groupe Mapping 1 : entre le modèle logique métier de l'en-tête et l'élément CDA clinicalDocument
+ - Groupe Mapping 2 : entre l'élément CDA clinicalDocument et le profil FHIR FrBundleDocument
+ - Groupe Mapping 3 : entre l'élément CDA clinicalDocument et le profil FHIR FrCompositionDocument</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
+++ b/htr-FHIR/ig/mappingmodelemetierCDAFHIR.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
